--- a/data/trans_camb/P1001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,97</t>
+          <t>0,23; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,16</t>
+          <t>-0,63; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,76</t>
+          <t>-1,08; 3,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,67</t>
+          <t>5,39; 11,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,27</t>
+          <t>2,74; 9,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,63</t>
+          <t>1,23; 6,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,46</t>
+          <t>3,52; 7,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,87</t>
+          <t>1,83; 5,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,48</t>
+          <t>0,78; 4,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 144,2</t>
+          <t>3,04; 152,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 123,47</t>
+          <t>-14,72; 127,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 126,77</t>
+          <t>-22,55; 101,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,52; 221,64</t>
+          <t>66,56; 232,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,19; 176,0</t>
+          <t>32,31; 177,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 121,71</t>
+          <t>13,43; 129,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,07; 157,3</t>
+          <t>54,71; 166,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,7; 126,59</t>
+          <t>28,79; 119,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,0; 96,12</t>
+          <t>12,16; 91,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,67</t>
+          <t>-0,26; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,94</t>
+          <t>-3,08; 0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,38</t>
+          <t>-4,83; 0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,15</t>
+          <t>5,48; 11,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,33</t>
+          <t>1,46; 7,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,9</t>
+          <t>0,89; 5,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,08</t>
+          <t>3,36; 6,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,46</t>
+          <t>0,04; 3,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,35</t>
+          <t>-2,25; 2,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 92,75</t>
+          <t>-5,31; 89,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 19,1</t>
+          <t>-44,44; 19,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,22; 6,21</t>
+          <t>-65,88; 5,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,86; 182,32</t>
+          <t>58,07; 173,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 117,56</t>
+          <t>14,46; 112,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 92,79</t>
+          <t>9,42; 94,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,29; 116,74</t>
+          <t>43,9; 118,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 56,58</t>
+          <t>0,51; 58,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 38,88</t>
+          <t>-29,71; 35,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,96</t>
+          <t>-4,75; 0,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,55</t>
+          <t>-4,05; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,77</t>
+          <t>-1,65; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,6</t>
+          <t>-3,56; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,13</t>
+          <t>-4,0; 3,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; -0,56</t>
+          <t>-10,42; -0,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,11</t>
+          <t>-3,29; 1,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,34</t>
+          <t>-3,12; 1,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,82</t>
+          <t>-5,26; 1,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 19,3</t>
+          <t>-53,79; 17,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,69; 26,25</t>
+          <t>-45,89; 25,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 83,58</t>
+          <t>-20,74; 83,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 30,38</t>
+          <t>-24,37; 28,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 26,19</t>
+          <t>-26,7; 28,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,35; -4,82</t>
+          <t>-69,01; -4,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 12,2</t>
+          <t>-28,15; 12,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 14,96</t>
+          <t>-26,92; 14,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 9,19</t>
+          <t>-44,72; 10,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,34</t>
+          <t>-1,34; 3,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,42</t>
+          <t>-1,26; 3,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,58</t>
+          <t>-2,88; 1,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,9</t>
+          <t>1,23; 7,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,19</t>
+          <t>-1,74; 3,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,45</t>
+          <t>-1,75; 4,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,31</t>
+          <t>0,62; 4,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,87</t>
+          <t>-0,91; 2,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,68</t>
+          <t>-1,13; 2,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 60,41</t>
+          <t>-17,48; 66,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 65,05</t>
+          <t>-16,75; 70,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 31,02</t>
+          <t>-37,17; 30,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,64; 75,26</t>
+          <t>9,88; 79,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 46,57</t>
+          <t>-15,13; 43,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 48,18</t>
+          <t>-14,94; 50,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,37; 57,2</t>
+          <t>6,23; 60,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 36,78</t>
+          <t>-9,69; 38,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 34,79</t>
+          <t>-12,13; 33,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,44</t>
+          <t>-0,15; 2,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,14</t>
+          <t>-1,08; 1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,98</t>
+          <t>-1,89; 0,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,87</t>
+          <t>3,75; 6,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,28</t>
+          <t>1,32; 4,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,87</t>
+          <t>-0,79; 3,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,23</t>
+          <t>2,18; 4,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,46</t>
+          <t>0,53; 2,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,68</t>
+          <t>-0,68; 1,74</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 44,46</t>
+          <t>-2,56; 41,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 21,42</t>
+          <t>-15,92; 20,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 17,42</t>
+          <t>-29,18; 17,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,5; 79,08</t>
+          <t>37,03; 80,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,65; 49,13</t>
+          <t>13,1; 51,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,27</t>
+          <t>-8,1; 33,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,84; 57,87</t>
+          <t>26,56; 57,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,11; 33,39</t>
+          <t>6,18; 33,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 22,98</t>
+          <t>-8,36; 23,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,94</t>
+          <t>0,14; 5,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,11</t>
+          <t>-0,87; 3,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,53</t>
+          <t>-1,04; 3,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,96</t>
+          <t>4,87; 11,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,2</t>
+          <t>2,87; 9,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,58</t>
+          <t>1,62; 6,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,74</t>
+          <t>3,43; 7,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,7</t>
+          <t>1,63; 5,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,3</t>
+          <t>0,9; 4,41</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 152,71</t>
+          <t>1,76; 148,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 127,31</t>
+          <t>-17,68; 120,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 101,25</t>
+          <t>-20,65; 111,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,56; 232,87</t>
+          <t>60,89; 212,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,31; 177,93</t>
+          <t>34,91; 170,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 129,16</t>
+          <t>19,63; 124,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,71; 166,67</t>
+          <t>52,93; 162,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 119,87</t>
+          <t>24,54; 130,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,16; 91,69</t>
+          <t>14,48; 97,38</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,52</t>
+          <t>-0,24; 4,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,93</t>
+          <t>-3,29; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,34</t>
+          <t>-2,76; 1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,05</t>
+          <t>5,23; 11,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,28</t>
+          <t>1,34; 7,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,83</t>
+          <t>0,81; 5,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,99</t>
+          <t>3,25; 7,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,48</t>
+          <t>-0,15; 3,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,16</t>
+          <t>-0,24; 3,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-30,97%</t>
+          <t>-11,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 89,87</t>
+          <t>-5,32; 92,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 19,13</t>
+          <t>-45,73; 21,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,88; 5,2</t>
+          <t>-39,32; 25,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,07; 173,69</t>
+          <t>57,74; 182,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 112,71</t>
+          <t>14,72; 113,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 94,09</t>
+          <t>9,63; 94,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,9; 118,91</t>
+          <t>40,97; 119,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 58,08</t>
+          <t>-2,23; 57,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 35,02</t>
+          <t>-3,47; 50,21</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,95</t>
+          <t>-4,76; 0,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,48</t>
+          <t>-4,14; 1,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,98</t>
+          <t>-2,07; 4,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,32</t>
+          <t>-4,15; 3,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,32</t>
+          <t>-3,95; 2,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -0,44</t>
+          <t>-4,36; 2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,17</t>
+          <t>-3,3; 1,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,38</t>
+          <t>-3,21; 1,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,04</t>
+          <t>-2,62; 1,94</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,76%</t>
+          <t>-9,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-14,68%</t>
+          <t>-2,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,79; 17,79</t>
+          <t>-54,2; 19,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 25,51</t>
+          <t>-46,04; 24,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 83,99</t>
+          <t>-24,64; 64,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 28,52</t>
+          <t>-26,61; 26,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 28,37</t>
+          <t>-26,48; 26,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,01; -4,6</t>
+          <t>-29,15; 19,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 12,99</t>
+          <t>-28,62; 15,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 14,71</t>
+          <t>-27,17; 17,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 10,65</t>
+          <t>-22,98; 21,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,46</t>
+          <t>-1,65; 3,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,6</t>
+          <t>-1,54; 3,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,66</t>
+          <t>-3,12; 1,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,01</t>
+          <t>1,43; 7,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,84</t>
+          <t>-1,99; 3,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,65</t>
+          <t>-0,07; 4,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,65</t>
+          <t>0,72; 4,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,9</t>
+          <t>-0,65; 2,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,64</t>
+          <t>-0,88; 2,46</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,09%</t>
+          <t>-14,5%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 66,53</t>
+          <t>-21,08; 60,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 70,01</t>
+          <t>-19,39; 62,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 30,68</t>
+          <t>-41,35; 20,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,88; 79,44</t>
+          <t>12,2; 80,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 43,29</t>
+          <t>-16,88; 42,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 50,71</t>
+          <t>-0,81; 53,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 60,89</t>
+          <t>7,25; 58,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 38,4</t>
+          <t>-7,14; 38,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 33,08</t>
+          <t>-9,19; 31,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,3</t>
+          <t>-0,16; 2,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,14</t>
+          <t>-1,19; 1,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,96</t>
+          <t>-1,21; 1,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,91</t>
+          <t>3,6; 6,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,35</t>
+          <t>1,19; 4,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,0</t>
+          <t>0,89; 3,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,23</t>
+          <t>2,15; 4,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,42</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,74</t>
+          <t>0,32; 2,24</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,9%</t>
+          <t>-0,26%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 41,44</t>
+          <t>-2,44; 44,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 20,12</t>
+          <t>-18,07; 21,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 17,48</t>
+          <t>-18,36; 21,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,03; 80,95</t>
+          <t>35,14; 75,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,1; 51,36</t>
+          <t>11,89; 51,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 33,81</t>
+          <t>8,65; 41,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,56; 57,2</t>
+          <t>25,88; 58,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,18; 33,07</t>
+          <t>6,0; 32,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 23,3</t>
+          <t>3,79; 31,43</t>
         </is>
       </c>
     </row>
